--- a/08_tables/q9_country_heterogeneity_fd_twfe.xlsx
+++ b/08_tables/q9_country_heterogeneity_fd_twfe.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/08_tables/q9_country_heterogeneity_fd_twfe.xlsx
+++ b/08_tables/q9_country_heterogeneity_fd_twfe.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Dependent variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Transformation</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Individual name (i)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>T(i)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>r(Y,X)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sigma(Y)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sigma(X)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sigma(Y)/sigma(X)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>beta = r * sigma(Y)/sigma(X)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
@@ -500,7 +488,7 @@
         <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>0.510324911410538</v>
+        <v>0.5103249114105377</v>
       </c>
       <c r="F2" t="n">
         <v>1.421560175769334</v>
@@ -512,7 +500,7 @@
         <v>0.6544690743989662</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3339918724135892</v>
+        <v>0.333991872413589</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -592,7 +580,7 @@
         <v>0.3318402519876755</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0526523284361471</v>
+        <v>0.05265232843614712</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -672,7 +660,7 @@
         <v>0.6568504183679437</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07770667363197056</v>
+        <v>0.07770667363197052</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -700,7 +688,7 @@
         <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09336962555361185</v>
+        <v>0.09336962555361182</v>
       </c>
       <c r="F7" t="n">
         <v>1.083821187902752</v>
@@ -712,7 +700,7 @@
         <v>0.6784585628398511</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06334742196599853</v>
+        <v>0.0633474219659985</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -740,7 +728,7 @@
         <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04608782076258403</v>
+        <v>0.04608782076258409</v>
       </c>
       <c r="F8" t="n">
         <v>1.963867920936729</v>
@@ -752,7 +740,7 @@
         <v>1.27456325171844</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05874184269577574</v>
+        <v>0.05874184269577581</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -780,7 +768,7 @@
         <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01647387639262549</v>
+        <v>0.01647387639262551</v>
       </c>
       <c r="F9" t="n">
         <v>1.014478519568879</v>
@@ -792,7 +780,7 @@
         <v>0.5862105327598844</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00965715985674147</v>
+        <v>0.009657159856741482</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -820,7 +808,7 @@
         <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02969434933255636</v>
+        <v>-0.02969434933255633</v>
       </c>
       <c r="F10" t="n">
         <v>0.7963725156441988</v>
@@ -832,7 +820,7 @@
         <v>0.4300284673672654</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01276941553294739</v>
+        <v>-0.01276941553294738</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -900,7 +888,7 @@
         <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1353450591853307</v>
+        <v>-0.1353450591853306</v>
       </c>
       <c r="F12" t="n">
         <v>0.7640353394968061</v>
@@ -912,7 +900,7 @@
         <v>0.4527487870650821</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06127731138141022</v>
+        <v>-0.06127731138141018</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -940,7 +928,7 @@
         <v>49</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1979163773863493</v>
+        <v>-0.1979163773863492</v>
       </c>
       <c r="F13" t="n">
         <v>2.678671426704832</v>
@@ -952,7 +940,7 @@
         <v>1.395224651218623</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2761378086093226</v>
+        <v>-0.2761378086093225</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -980,7 +968,7 @@
         <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2084642043158378</v>
+        <v>-0.208464204315838</v>
       </c>
       <c r="F14" t="n">
         <v>0.955386626158319</v>
@@ -992,7 +980,7 @@
         <v>0.4860310484329579</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.101320075784369</v>
+        <v>-0.1013200757843691</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1020,7 +1008,7 @@
         <v>49</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.214721280449806</v>
+        <v>-0.2147212804498059</v>
       </c>
       <c r="F15" t="n">
         <v>0.9847605807304358</v>
@@ -1032,7 +1020,7 @@
         <v>0.446318005483476</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.09583397362521549</v>
+        <v>-0.09583397362521545</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1100,7 +1088,7 @@
         <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5843878752776019</v>
+        <v>0.5843878752776017</v>
       </c>
       <c r="F17" t="n">
         <v>2.318213332948363</v>
@@ -1112,7 +1100,7 @@
         <v>1.432874321866217</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8373543804952334</v>
+        <v>0.8373543804952331</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1140,7 +1128,7 @@
         <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4796868568595204</v>
+        <v>0.4796868568595203</v>
       </c>
       <c r="F18" t="n">
         <v>2.171745934495637</v>
@@ -1152,7 +1140,7 @@
         <v>0.9962013318926154</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4778646856948366</v>
+        <v>0.4778646856948365</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1180,7 +1168,7 @@
         <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4152058736231807</v>
+        <v>0.4152058736231806</v>
       </c>
       <c r="F19" t="n">
         <v>2.430031241068674</v>
@@ -1192,7 +1180,7 @@
         <v>1.596174571509056</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6627410574185235</v>
+        <v>0.6627410574185234</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1300,7 +1288,7 @@
         <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1864719104597827</v>
+        <v>0.1864719104597828</v>
       </c>
       <c r="F22" t="n">
         <v>1.278923994909921</v>
@@ -1312,7 +1300,7 @@
         <v>0.5260501505363546</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09809357656817033</v>
+        <v>0.09809357656817036</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1340,7 +1328,7 @@
         <v>50</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1777081084621943</v>
+        <v>0.1777081084621944</v>
       </c>
       <c r="F23" t="n">
         <v>1.832622727124983</v>
@@ -1352,7 +1340,7 @@
         <v>1.251725579272677</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2224417850062919</v>
+        <v>0.222441785006292</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1420,7 +1408,7 @@
         <v>50</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1175306650665298</v>
+        <v>0.1175306650665297</v>
       </c>
       <c r="F25" t="n">
         <v>2.937890388957019</v>
@@ -1460,7 +1448,7 @@
         <v>50</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06451535393105784</v>
+        <v>0.06451535393105777</v>
       </c>
       <c r="F26" t="n">
         <v>1.437370431297379</v>
@@ -1472,7 +1460,7 @@
         <v>0.7543420113352126</v>
       </c>
       <c r="I26" t="n">
-        <v>0.04866664184635729</v>
+        <v>0.04866664184635723</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1500,7 +1488,7 @@
         <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.02113118234055541</v>
+        <v>-0.02113118234055547</v>
       </c>
       <c r="F27" t="n">
         <v>2.010226608182081</v>
@@ -1512,7 +1500,7 @@
         <v>1.590342363845995</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.03360581447433963</v>
+        <v>-0.03360581447433973</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1540,7 +1528,7 @@
         <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1193867967532351</v>
+        <v>-0.119386796753235</v>
       </c>
       <c r="F28" t="n">
         <v>1.46974698698368</v>
@@ -1552,7 +1540,7 @@
         <v>1.591124515816842</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.189959259178915</v>
+        <v>-0.1899592591789148</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1580,7 +1568,7 @@
         <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2815675730156755</v>
+        <v>-0.2815675730156753</v>
       </c>
       <c r="F29" t="n">
         <v>6.15190922474785</v>
@@ -1592,7 +1580,7 @@
         <v>1.701477183942436</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4790808012242178</v>
+        <v>-0.4790808012242174</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1620,7 +1608,7 @@
         <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4743324565163199</v>
+        <v>-0.4743324565163202</v>
       </c>
       <c r="F30" t="n">
         <v>1.208114906988624</v>
@@ -1632,7 +1620,7 @@
         <v>0.6414017097702938</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3042376486091111</v>
+        <v>-0.3042376486091113</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1712,7 +1700,7 @@
         <v>0.4580657184669295</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08953702458995021</v>
+        <v>0.08953702458995019</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1740,7 +1728,7 @@
         <v>49</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1846492518103717</v>
+        <v>0.1846492518103718</v>
       </c>
       <c r="F33" t="n">
         <v>0.8734073328871145</v>
@@ -1752,7 +1740,7 @@
         <v>0.5000721715463334</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09233795232721832</v>
+        <v>0.09233795232721836</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1780,7 +1768,7 @@
         <v>49</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1667160351249375</v>
+        <v>0.1667160351249376</v>
       </c>
       <c r="F34" t="n">
         <v>0.9533086976519278</v>
@@ -1792,7 +1780,7 @@
         <v>0.5649075824748649</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09417915236222311</v>
+        <v>0.09417915236222316</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1860,7 +1848,7 @@
         <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04106033386911546</v>
+        <v>0.04106033386911545</v>
       </c>
       <c r="F36" t="n">
         <v>2.330821550258769</v>
@@ -1872,7 +1860,7 @@
         <v>1.209890131238988</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04967849273362076</v>
+        <v>0.04967849273362074</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1912,7 +1900,7 @@
         <v>0.2984143035499193</v>
       </c>
       <c r="I37" t="n">
-        <v>0.007420569021618246</v>
+        <v>0.007420569021618248</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1940,7 +1928,7 @@
         <v>49</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.02391609553551935</v>
+        <v>-0.02391609553551932</v>
       </c>
       <c r="F38" t="n">
         <v>1.386817607353463</v>
@@ -1952,7 +1940,7 @@
         <v>0.8681305470939505</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0207622931016016</v>
+        <v>-0.02076229310160158</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1980,7 +1968,7 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.05912399327769081</v>
+        <v>-0.0591239932776908</v>
       </c>
       <c r="F39" t="n">
         <v>1.229586591448442</v>
@@ -1992,7 +1980,7 @@
         <v>0.735664780164847</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.04349543951710031</v>
+        <v>-0.0434954395171003</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2020,7 +2008,7 @@
         <v>49</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.08545533251701325</v>
+        <v>-0.08545533251701327</v>
       </c>
       <c r="F40" t="n">
         <v>2.013552755355238</v>
@@ -2060,7 +2048,7 @@
         <v>49</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.09727887386176774</v>
+        <v>-0.09727887386176777</v>
       </c>
       <c r="F41" t="n">
         <v>2.722877153070094</v>
@@ -2100,7 +2088,7 @@
         <v>49</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1098564659120684</v>
+        <v>-0.1098564659120685</v>
       </c>
       <c r="F42" t="n">
         <v>1.983653846823909</v>
@@ -2112,7 +2100,7 @@
         <v>0.9132501874964233</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1003264380918909</v>
+        <v>-0.100326438091891</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2140,7 +2128,7 @@
         <v>49</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2190376817082401</v>
+        <v>-0.2190376817082402</v>
       </c>
       <c r="F43" t="n">
         <v>1.019636176988596</v>
@@ -2152,7 +2140,7 @@
         <v>0.5187165348071534</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1136184672478905</v>
+        <v>-0.1136184672478906</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2180,7 +2168,7 @@
         <v>49</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.2654418009640542</v>
+        <v>-0.2654418009640543</v>
       </c>
       <c r="F44" t="n">
         <v>3.6122766572859</v>
@@ -2192,7 +2180,7 @@
         <v>1.637173689201197</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4345743325525305</v>
+        <v>-0.4345743325525306</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2220,7 +2208,7 @@
         <v>49</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.3027669220349306</v>
+        <v>-0.3027669220349305</v>
       </c>
       <c r="F45" t="n">
         <v>10.6994040425136</v>
@@ -2232,7 +2220,7 @@
         <v>5.572938929589782</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.687301566400539</v>
+        <v>-1.687301566400538</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2260,7 +2248,7 @@
         <v>50</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3039842726893356</v>
+        <v>0.3039842726893355</v>
       </c>
       <c r="F46" t="n">
         <v>23.84141911556899</v>
@@ -2272,7 +2260,7 @@
         <v>10.9362946649907</v>
       </c>
       <c r="I46" t="n">
-        <v>3.32446157965346</v>
+        <v>3.324461579653459</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2312,7 +2300,7 @@
         <v>3.440305030481115</v>
       </c>
       <c r="I47" t="n">
-        <v>0.766085885445826</v>
+        <v>0.7660858854458257</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2340,7 +2328,7 @@
         <v>50</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2139789310142514</v>
+        <v>0.2139789310142513</v>
       </c>
       <c r="F48" t="n">
         <v>4.099917828438966</v>
@@ -2352,7 +2340,7 @@
         <v>2.796493935371719</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5983907828786774</v>
+        <v>0.5983907828786771</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2392,7 +2380,7 @@
         <v>6.725236262178879</v>
       </c>
       <c r="I49" t="n">
-        <v>1.287510553871072</v>
+        <v>1.287510553871073</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2460,7 +2448,7 @@
         <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1147287161564475</v>
+        <v>0.1147287161564476</v>
       </c>
       <c r="F51" t="n">
         <v>14.11162384810581</v>
@@ -2472,7 +2460,7 @@
         <v>5.559357427509847</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6378179403130154</v>
+        <v>0.6378179403130156</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2500,7 +2488,7 @@
         <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>0.05854856846911444</v>
+        <v>0.05854856846911441</v>
       </c>
       <c r="F52" t="n">
         <v>15.16997759265883</v>
@@ -2512,7 +2500,7 @@
         <v>15.67691971428854</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9178612072768324</v>
+        <v>0.917861207276832</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2540,7 +2528,7 @@
         <v>50</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.06092761473305858</v>
+        <v>-0.06092761473305861</v>
       </c>
       <c r="F53" t="n">
         <v>12.97165206594206</v>
@@ -2552,7 +2540,7 @@
         <v>5.335531704114017</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3250812200642784</v>
+        <v>-0.3250812200642785</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2592,7 +2580,7 @@
         <v>4.979013733795616</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5409223371324662</v>
+        <v>-0.5409223371324658</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2620,7 +2608,7 @@
         <v>50</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1843956436203497</v>
+        <v>-0.1843956436203499</v>
       </c>
       <c r="F55" t="n">
         <v>46.88030845688544</v>
@@ -2632,7 +2620,7 @@
         <v>12.9660195398679</v>
       </c>
       <c r="I55" t="n">
-        <v>-2.390877518247972</v>
+        <v>-2.390877518247975</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2660,7 +2648,7 @@
         <v>50</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2048817242754179</v>
+        <v>-0.204881724275418</v>
       </c>
       <c r="F56" t="n">
         <v>9.445117146899639</v>
@@ -2712,7 +2700,7 @@
         <v>2.485224654413162</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6502761962142498</v>
+        <v>-0.65027619621425</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2740,7 +2728,7 @@
         <v>50</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3365576363702834</v>
+        <v>-0.3365576363702831</v>
       </c>
       <c r="F58" t="n">
         <v>8.597946471517425</v>
@@ -2752,7 +2740,7 @@
         <v>9.307998953335629</v>
       </c>
       <c r="I58" t="n">
-        <v>-3.13267812707171</v>
+        <v>-3.132678127071708</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2780,7 +2768,7 @@
         <v>50</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4020073820963944</v>
+        <v>-0.4020073820963943</v>
       </c>
       <c r="F59" t="n">
         <v>7.932583708025636</v>
